--- a/Outputs/Scenarios/PtX_demand_LV_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LV_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001613032710587493</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004519925482466532</v>
+        <v>0.002448378737498126</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001506641827488844</v>
+        <v>0.003559381279962267</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>2.324107095311647e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001506641827488844</v>
+        <v>0.001525449119983829</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002387898547100426</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0243967253584058</v>
+        <v>0.0132153558424388</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.008132241786135266</v>
+        <v>0.01921209716176627</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001256788709000225</v>
       </c>
       <c r="K42" t="n">
-        <v>0.008132241786135266</v>
+        <v>0.00823375592647126</v>
       </c>
     </row>
     <row r="43">
